--- a/123.xlsx
+++ b/123.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hoodes</t>
+          <t>Hoodies</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hoodes</t>
+          <t>Hoodies</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hoodes</t>
+          <t>Hoodies</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hoodes</t>
+          <t>Hoodies</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hoodes</t>
+          <t>Hoodies</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hoodes</t>
+          <t>Hoodies</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hoodes</t>
+          <t>Hoodies</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hoodes</t>
+          <t>Hoodies</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hoodes</t>
+          <t>Hoodies</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hoodes</t>
+          <t>Hoodies</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hoodes</t>
+          <t>Hoodies</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hoodes</t>
+          <t>Hoodies</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hoodes</t>
+          <t>Hoodies</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hoodes</t>
+          <t>Hoodies</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hoodes</t>
+          <t>Hoodies</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hoodes</t>
+          <t>Hoodies</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hoodes</t>
+          <t>Hoodies</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hoodes</t>
+          <t>Hoodies</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hoodes</t>
+          <t>Hoodies</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hoodes</t>
+          <t>Hoodies</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hoodes</t>
+          <t>Hoodies</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Hoodes</t>
+          <t>Hoodies</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
